--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-valparaiso.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/region-de-valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2487-32-CM26</t>
+          <t>2026-1555-CM24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>16293.69</v>
+        <v>9825.309999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1725-673-CM26</t>
+          <t>956-44-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>61.606.500-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11498.91</v>
+        <v>8513.440000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1208983-197-CM26</t>
+          <t>2026-340-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,43 +691,43 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17988.57</v>
+        <v>77883.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1216085-299-CM26</t>
+          <t>2026-1385-CM24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.983.600-5</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL PARA EL DESARROLLO SOCIAL</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>MUEBLES ANDROMEDA DOS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.285.439-0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7322.64</v>
+        <v>41725.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4895-199-CM26</t>
+          <t>1305525-17-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.981.120-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EASTON LIMITADA</t>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.028.554-4</t>
+          <t>77.351.814-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,43 +813,43 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9941.32</v>
+        <v>5656.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1305525-193-CM26</t>
+          <t>2026-135-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.981.120-8</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>OLLER Y CIA LTDA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>88.041.000-8</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,6 +874,2019 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
+        <v>60015.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2428-363-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.061.300-K</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>12927.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1057370-2072-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.602.040-4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>5919.33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-593-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>61.606.600-5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>9478.870000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-658-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.606.600-5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>5564.65</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-680-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.606.600-5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>6935.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-693-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.606.600-5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>78.616.370-6</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>10231.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-694-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.606.600-5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>7515.47</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1305525-41-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.981.120-8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>15287.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4014-217-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>8565.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2945-534-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.102.004-K</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>17864.82</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2176-305-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>22830.81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3108-53-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.926.100-3</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>5810.64</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>859378-309-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>31975.79</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1351-63-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.002.012-7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>7750.41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4895-118-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>OFISILLAS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>8503.15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1080157-88-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.979.360-9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>78.616.370-6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>5944.05</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2832-710-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>69.260.400-8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>19483.15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1413007-66-CM25</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>60.804.007-2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>11270.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1231-45-CM25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>60.804.008-0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CLOUDBOOK SPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.399.128-8</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>5685.73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3275-262-CM25</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>21332.64</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3275-261-CM25</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.235.755-0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>14119.12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3275-263-CM25</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.235.755-0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>18024.74</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2176-431-CM25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>13466.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4844-147-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.073.700-0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>36881.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2832-887-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.260.400-8</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Plusmedical SpA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>76.520.087-3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>13542.23</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1413021-63-CM25</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>60.804.011-0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>IGMA CONSULTORES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>76.465.697-0</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>7896.54</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1413007-87-CM25</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>60.804.007-2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>6757.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2487-32-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>16293.69</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1725-673-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>60.901.002-9</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.058.118-6</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>11498.91</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1208983-197-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>17988.57</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4895-199-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>EASTON LIMITADA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.028.554-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>9941.32</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1216085-299-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>70.983.600-5</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL PARA EL DESARROLLO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>7322.64</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1305525-193-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.981.120-8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
         <v>60969.44</v>
       </c>
     </row>
